--- a/docs/SECS/SECS_GEM功能_Handler_20260803.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260803.xlsx
@@ -286,7 +286,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -464,6 +464,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -922,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="26" min="1" max="1"/>
@@ -1588,7 +1597,7 @@
       </c>
       <c r="B64" s="64" t="inlineStr">
         <is>
-          <t>與第 1 點同源的三個編號對齊項，本版尚未實作，待貴端確認是否需要：HT9045 以 SVID 4 GemControlState(1=Off-Line / 2=On-Line Local / 3=On-Line Remote)與 SVID 9 PreviousGemControlState 公佈控制狀態，並在狀態變更時送 CEID 141(GEM Control State Change)與CEID 91/92/93(Offline / Online Local / Online Remote)。本機目前把同一資訊放在自有的 SVID 66002(採 GEM 標準值域 1/4/5)，且 CEID 141 與 91/92/93 已註冊但無發射點。依來信第 3 點的原則，這四個號碼應改為與 HT9045 同號同值域。</t>
+          <t>(2026-08-03 已實作，見本表末「第 4 版 追加項」)原內容：HT9045 以 SVID 4 / 9 公佈控制狀態並在變更時發 CEID 141 與 91/92/93，本機當時只有自有的 SVID 66002 且那四個 CEID 無發射點。依貴端來信第 3 點的原則，本機已補上同號同值域的 SVID 4 / 9 與四個事件發射點。</t>
         </is>
       </c>
     </row>
@@ -1625,6 +1634,83 @@
       <c r="B67" s="64" t="inlineStr">
         <is>
           <t>模擬版與真機版(註銷 SOFT_SIMULATE)建置皆 exit 0，還原後再建置亦 exit 0，原始碼編碼檢查 166 檔通過。另以 headless SECS host 對實際韌體(EXE\ht160s.exe)做 HSMS round-trip 實測：S1F3 查 19 個新號碼全部回真值且型別正確；以貴端 2026-07-31 的真實報表定義重建 RPTID 501/502/513/800 後用 S6F19 拉取，得 501 = 5/12、502 = 6/8、513 = 0/6、tray 幾何 6/6;SET_LOT_INFO + LOTSTART 後 1009 回 '2026-08-03 00:58:00'、66033 回 '2026/08/03 00:58:00'(同一時刻兩種格式)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="62" t="n"/>
+      <c r="B68" s="64" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="62" t="inlineStr">
+        <is>
+          <t>2026-08-03 第 4 版 追加項(同日，承第 4 版)</t>
+        </is>
+      </c>
+      <c r="B69" s="64" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="62" t="inlineStr">
+        <is>
+          <t>依據韌體 Firmware</t>
+        </is>
+      </c>
+      <c r="B70" s="64" t="inlineStr">
+        <is>
+          <t>HT-160S 1.0.0.0, branch feat/iosetview-172-refactor (SVID 4/9 + CEID 141/91/92/93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="62" t="inlineStr">
+        <is>
+          <t>6. 控制狀態改用 HT-90XX 編號(回應來信第 3 點)</t>
+        </is>
+      </c>
+      <c r="B71" s="64" t="inlineStr">
+        <is>
+          <t>依「相同功能使用同一編號」的原則，控制狀態改以 HT9045 的號碼與值域公佈：
+• 新增 SVID 4 GemControlState，型別 U1，值域 1=Off-Line / 2=On-Line Local / 3=On-Line Remote(與 HT9045 完全相同，非 GEM 標準的 1/4/5)。
+• 新增 SVID 9 PreviousGemControlState，型別 U1，值域同上，內容為變更前的狀態。
+• 狀態每次變更時先送 CEID 141 GEM Control State Change，緊接著依新狀態再送 CEID 91(Offline) / 92(Online Local) / 93(Online Remote) 之一 —— 順序與 HT9045 相同。這四個號碼先前已註冊但無發射點。
+• 既有的 SVID 66002 Control State 保留不變(GEM 標準值域 1/4/5)。同一個狀態以兩種編號公佈，兩者恆等；9045 編號的 host 請改讀 SVID 4。之所以不直接改 66002 的值域，是因為該號碼已在前版規格書對貴端公佈，變更值域會讓既有設定靜默誤讀。
+• CEID 表中 91 / 92 / 93 / 141 四列已由「—(不會發射)」改為「★ 會發射」，本機會發射的號碼由 52 增為 56(另有 1 個條件發射的 78，合計 57 個有發射點)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="62" t="inlineStr">
+        <is>
+          <t>7. 更正前版一處錯誤敘述</t>
+        </is>
+      </c>
+      <c r="B72" s="64" t="inlineStr">
+        <is>
+          <t>CEID 表中 91 / 92 / 93 / 141 的備註原寫「HT9045 韌體同樣只宣告不發射」，該敘述錯誤。HT9045 這四個號碼的發射點在其框架層的控制狀態變更區塊(以字面值呼叫 EventReport)，前次盤點只掃應用層檔案因此漏判。備註已更正。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="62" t="inlineStr">
+        <is>
+          <t>追加項的驗證 Verification</t>
+        </is>
+      </c>
+      <c r="B73" s="64" t="inlineStr">
+        <is>
+          <t>模擬版 -Full、真機版(註銷 SOFT_SIMULATE)-Full、還原後再 -Full 三次建置皆 exit 0，原始碼編碼檢查 166 檔通過。另以 headless SECS host 對實際韌體做 HSMS round-trip 實測，逐一驗證狀態轉移與事件：開機 SVID 4=1 / SVID 9=1；收 S1F17 後 4=3、9=1，並收到 CEID 141 與 93；下 ONLINE_LOCAL 後 4=2、9=3，收到 141 與 92；收 S1F15 後 4=1、9=2，收到 141 與 91；再次送 S1F15(狀態未變)則不再發射任何事件(邊緣觸發正確)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="62" t="inlineStr">
+        <is>
+          <t>尚待貴端確認 Still open</t>
+        </is>
+      </c>
+      <c r="B74" s="64" t="inlineStr">
+        <is>
+          <t>來信第 1 點的命令閘門(本表 Open item 6)仍待貴端回答三個問題後才能實作：Off-Line 要拒絕哪些命令(全部，或保留 ONLINE_* 類以免無法上線)、拒絕時回哪個 HCACK、On-Line Local 是否也要拒絕。本追加項只補「狀態的公佈與通知」，未改變「命令是否受理」的行為。</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="6.5" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
@@ -3857,6 +3943,26 @@
       <c r="B78" s="62" t="inlineStr">
         <is>
           <t>Auto6 Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" s="62" t="inlineStr">
+        <is>
+          <t>GemControlState</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="62" t="n">
+        <v>9</v>
+      </c>
+      <c r="B80" s="62" t="inlineStr">
+        <is>
+          <t>PreviousGemControlState</t>
         </is>
       </c>
     </row>
@@ -5951,65 +6057,77 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="41" t="n">
+      <c r="A92" s="65" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="42" t="inlineStr">
+      <c r="B92" s="66" t="inlineStr">
         <is>
           <t>SECS/GEM Offline</t>
         </is>
       </c>
-      <c r="C92" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D92" s="42" t="inlineStr"/>
-      <c r="E92" s="42" t="inlineStr">
-        <is>
-          <t>HT9045 韌體同樣只宣告不發射(115 的唯一站點在 9045 被註解)，無可對照的觸發時機</t>
+      <c r="C92" s="65" t="inlineStr">
+        <is>
+          <t>★ 會發射</t>
+        </is>
+      </c>
+      <c r="D92" s="66" t="inlineStr">
+        <is>
+          <t>Report 1</t>
+        </is>
+      </c>
+      <c r="E92" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-03 新增發射點:GEM 控制狀態(Off-Line / On-Line Local / On-Line Remote)每次變更時，先送 CEID 141，緊接著依新狀態再送 91 / 92 / 93 之一，順序與 HT9045 相同。狀態值請讀 SVID 4 (1/2/3，HT9045 值域)與 SVID 9(變更前的值)。⚠ 更正前版敘述:前版備註寫「HT9045 韌體同樣只宣告不發射」是錯的 —— HT9045 的發射點在其框架層的控制狀態變更區塊，以字面值呼叫，前次盤點只掃應用層因此漏判。本機已與之對齊。</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="43" t="n">
+      <c r="A93" s="65" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="44" t="inlineStr">
+      <c r="B93" s="66" t="inlineStr">
         <is>
           <t>SECS/GEM Online</t>
         </is>
       </c>
-      <c r="C93" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D93" s="44" t="inlineStr"/>
-      <c r="E93" s="44" t="inlineStr">
-        <is>
-          <t>HT9045 韌體同樣只宣告不發射(115 的唯一站點在 9045 被註解)，無可對照的觸發時機</t>
+      <c r="C93" s="65" t="inlineStr">
+        <is>
+          <t>★ 會發射</t>
+        </is>
+      </c>
+      <c r="D93" s="66" t="inlineStr">
+        <is>
+          <t>Report 1</t>
+        </is>
+      </c>
+      <c r="E93" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-03 新增發射點:GEM 控制狀態(Off-Line / On-Line Local / On-Line Remote)每次變更時，先送 CEID 141，緊接著依新狀態再送 91 / 92 / 93 之一，順序與 HT9045 相同。狀態值請讀 SVID 4 (1/2/3，HT9045 值域)與 SVID 9(變更前的值)。⚠ 更正前版敘述:前版備註寫「HT9045 韌體同樣只宣告不發射」是錯的 —— HT9045 的發射點在其框架層的控制狀態變更區塊，以字面值呼叫，前次盤點只掃應用層因此漏判。本機已與之對齊。</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="41" t="n">
+      <c r="A94" s="65" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="42" t="inlineStr">
+      <c r="B94" s="66" t="inlineStr">
         <is>
           <t>SECS/GEM Online Remote</t>
         </is>
       </c>
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D94" s="42" t="inlineStr"/>
-      <c r="E94" s="42" t="inlineStr">
-        <is>
-          <t>HT9045 韌體同樣只宣告不發射(115 的唯一站點在 9045 被註解)，無可對照的觸發時機</t>
+      <c r="C94" s="65" t="inlineStr">
+        <is>
+          <t>★ 會發射</t>
+        </is>
+      </c>
+      <c r="D94" s="66" t="inlineStr">
+        <is>
+          <t>Report 1</t>
+        </is>
+      </c>
+      <c r="E94" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-03 新增發射點:GEM 控制狀態(Off-Line / On-Line Local / On-Line Remote)每次變更時，先送 CEID 141，緊接著依新狀態再送 91 / 92 / 93 之一，順序與 HT9045 相同。狀態值請讀 SVID 4 (1/2/3，HT9045 值域)與 SVID 9(變更前的值)。⚠ 更正前版敘述:前版備註寫「HT9045 韌體同樣只宣告不發射」是錯的 —— HT9045 的發射點在其框架層的控制狀態變更區塊，以字面值呼叫，前次盤點只掃應用層因此漏判。本機已與之對齊。</t>
         </is>
       </c>
     </row>
@@ -7021,23 +7139,27 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="41" t="n">
+      <c r="A142" s="65" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="42" t="inlineStr">
+      <c r="B142" s="66" t="inlineStr">
         <is>
           <t>GEM Control State Change</t>
         </is>
       </c>
-      <c r="C142" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D142" s="42" t="inlineStr"/>
-      <c r="E142" s="42" t="inlineStr">
-        <is>
-          <t>HT9045 韌體同樣只宣告不發射(115 的唯一站點在 9045 被註解)，無可對照的觸發時機</t>
+      <c r="C142" s="65" t="inlineStr">
+        <is>
+          <t>★ 會發射</t>
+        </is>
+      </c>
+      <c r="D142" s="66" t="inlineStr">
+        <is>
+          <t>Report 1</t>
+        </is>
+      </c>
+      <c r="E142" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-03 新增發射點:GEM 控制狀態(Off-Line / On-Line Local / On-Line Remote)每次變更時，先送 CEID 141，緊接著依新狀態再送 91 / 92 / 93 之一，順序與 HT9045 相同。狀態值請讀 SVID 4 (1/2/3，HT9045 值域)與 SVID 9(變更前的值)。⚠ 更正前版敘述:前版備註寫「HT9045 韌體同樣只宣告不發射」是錯的 —— HT9045 的發射點在其框架層的控制狀態變更區塊，以字面值呼叫，前次盤點只掃應用層因此漏判。本機已與之對齊。</t>
         </is>
       </c>
     </row>

--- a/docs/SECS/SECS_GEM功能_Handler_20260803.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260803.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="新細明體"/>
       <charset val="136"/>
@@ -105,6 +105,10 @@
       <name val="新細明體"/>
       <charset val="136"/>
       <family val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -236,7 +240,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -384,6 +388,9 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1493,9 +1500,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B63" s="40" t="inlineStr">
-        <is>
-          <t>來信第 1 點「Offline 情況下仍能下 Command」—— 已確認現況：本機的 S2F41 遠端命令處理不以 GEM 控制狀態(Off-Line / On-Line Local / On-Line Remote)為閘，任一狀態皆會受理並執行。附帶說明，作為對齊基準的 HT9045 同樣不設此閘(其原始碼中該閘僅對另一家客戶代碼生效)。若貴端要求依 GEM 規範在 Off-Line 拒絕命令，請確認：(a) Off-Line 時要拒絕哪些命令(全部，或保留 ONLINE 類命令)，(b) 拒絕時回哪個 HCACK，(c) On-Line Local 是否也要拒絕。確認後本機即可加閘。</t>
+      <c r="B63" s="56" t="inlineStr">
+        <is>
+          <t>來信第 1 點「Offline 情況下仍能下 Command」—— 已確認現況：本機的 S2F41 遠端命令處理不以 GEM 控制狀態(Off-Line / On-Line Local / On-Line Remote)為閘，任一狀態皆會受理並執行。與 HT9045 的對照(2026-08-03 逐段查證後更正)：HT9045 的 S2F41 處理器同樣沒有任何控制狀態檢查(其 S2F42 全函式查無 bOnLine / GemControlState)，這點兩機一致；但 HT9045 另有兩項本機沒有的機制——(1) 對 host 的 S1F17 有操作員否決權(已在線回 ONLACK=2、操作員勾選 AcceptHostOnlineRequest 才回 0、未勾選回 1 拒絕；本機一律硬回 0)；(2) 離線時不主動發送事件與警報。原句「其原始碼中該閘僅對另一家客戶代碼生效」只對「S/F 收訊閘門」成立，對上述兩項不成立。若貴端要求依 GEM 規範在 Off-Line 拒絕命令，請確認：(a) Off-Line 時要拒絕哪些命令(全部，或保留 ONLINE 類命令)，(b) 拒絕時回哪個 HCACK，(c) On-Line Local 是否也要拒絕。確認後本機即可加閘。</t>
         </is>
       </c>
     </row>

--- a/docs/SECS/SECS_GEM功能_Handler_20260803.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260803.xlsx
@@ -848,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" style="8" min="1" max="1"/>
@@ -862,6 +862,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -870,7 +871,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>2026-07-29 (第 1 版) / 2026-07-30 (第 2 版) / 2026-08-02 (第 3 版) / 2026-08-03 (第 4 版) / 2026-08-03 (第 4 版 追加項、追加項2，本次)</t>
+          <t>2026-07-29 (第 1 版) / 2026-07-30 (第 2 版) / 2026-08-02 (第 3 版) / 2026-08-03 (第 4 版) / 2026-08-03 (第 4 版 追加項、追加項2、追加項3、追加項4，本次)</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1027,7 @@
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>(2026-08-02 已解除)不再需要 HT9045 的 SVID 目錄傾印。2026-07-31 現場 log 已提供貴端 host 自己的完整需求清單(33 張 S2F33 報表定義、31 條 S2F35 連結、389 個相異 SVID)，比 9045 的目錄更權威。其中 AMR 相關報表為 RPTID 2000 = {38202, 38205, 38206, 38207, 38219, 38220, 38221} 與 RPTID 2001 = {38222-38236}，另 RPTID 524 = {38237, 38238, 38239}；38208-38210 / 38240-38245 這 9 個 Auto4-6 延伸號貴端完全未引用，本機仍照常註冊並可以 S1F3 回覆。⚠ 但 38237/38238/38239 這 3 個貴端已引用的號碼有語意疑慮：貴端把 RPTID 524 綁在 CEID 67 Tray Test Finish 上，而本機對這三個號碼的定義是「AMR AUTO4/5/6 Tray Count」，與 Tray Test Finish 不相稱；且 CEID 67 為測試機事件，HT-160S 不會發射，故該報表目前永遠不會送出。請貴端確認 9045 對這三個號碼的定義是否與本機一致，若不一致則需另行編號。此為本項唯一尚未關閉的部分。</t>
+          <t>(2026-08-02 已解除)不再需要 HT9045 的 SVID 目錄傾印。2026-07-31 現場 log 已提供貴端 host 自己的完整需求清單(33 張 S2F33 報表定義、31 條 S2F35 連結、389 個相異 SVID)，比 9045 的目錄更權威。其中 AMR 相關報表為 RPTID 2000 = {38202, 38205, 38206, 38207, 38219, 38220, 38221} 與 RPTID 2001 = {38222-38236}，另 RPTID 524 = {38237, 38238, 38239}；38208-38210 / 38240-38245 這 9 個 Auto4-6 延伸號貴端完全未引用，本機仍照常註冊並可以 S1F3 回覆〔註:38208-38210 已於同日「追加項5」第 18 項改號為 38199-38201;此處為當時的引用分析記錄，不予追改。併此確認:貴端 RPTID 2000 只引用 38205-38207，未引用 38208-38210，故該次改號不影響貴端任何既有報表定義〕。⚠ 但 38237/38238/38239 這 3 個貴端已引用的號碼有語意疑慮：貴端把 RPTID 524 綁在 CEID 67 Tray Test Finish 上，而本機對這三個號碼的定義是「AMR AUTO4/5/6 Tray Count」，與 Tray Test Finish 不相稱；且 CEID 67 為測試機事件，HT-160S 不會發射，故該報表目前永遠不會送出。請貴端確認 9045 對這三個號碼的定義是否與本機一致，若不一致則需另行編號。此為本項唯一尚未關閉的部分。</t>
         </is>
       </c>
     </row>
@@ -1274,6 +1275,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="28" t="inlineStr">
         <is>
@@ -1429,7 +1431,7 @@
 • 1103 / 1104 / 1105 Auto1-3 Count — 各 Auto 出料盤的放料數。
 • 1501 Setup File — 目前 recipe 名。註：同號的 ECID 1501 一直存在，但 SECS-II 的 SVID 與 ECID 是兩個獨立命名空間，而貴端是以 SVID 路徑讀它，故先前回空。本版在 SV 側補註冊同號、同型別、指向同一份資料。
 • 2758-2763 Type 1 Tray 幾何(Pitch X/Y、Start X/Y、Division X/Y) — 同 1501 的情況(原僅存在於 EC 側)。單位為 mm，與 HT9045 一致。
-• 66025-66027 Auto4-6 Count — 本機自有段，HT9045 無對應號碼的第 4-6 站(見第 4 項)。〔本版原另新增 66022-66024 Auto1-3 Count，已於同日「追加項2」移除 —— 與 1103-1105 同值，請改讀 1103 / 1104 / 1105，詳見該節〕</t>
+• 1259 / 1260 / 1261 Auto4-6 Count — 各 Auto 出料盤的放料數(見第 4 項)。〔本版原將這三站放在本機自有段 66025-66027，已於同日「追加項5」改用 HT-9011UC V3.33.899 的家族編號，請改讀 1259 / 1260 / 1261〕〔本版原另新增 66022-66024 Auto1-3 Count，已於同日「追加項2」移除 —— 與 1103-1105 同值，請改讀 1103 / 1104 / 1105，詳見該節〕</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1457,7 @@
         <is>
           <t>已解決。貴端截圖中的 RPTID 502 = {1006, 1007, 1011, 3, 1501, 1517, 1518, 1513}，2026-07-31 當天本機只答得出第 7 格(1518 Real/Dummy = I4 2)，其餘 7 格皆為空 item —— 與截圖完全一致。
 本版起 502 的 8 格中有 6 格有值：1006 批號、1011 機況文字、3 設備時鐘、1501 recipe 名、1517 Start Mode、1518 Real/Dummy。已以 headless SECS host 對實際韌體實測確認。
-剩下 2 格是機構上給不出來的，建議貴端自報表定義中移除：1007 Operator ID(本機無 host 端操作員身分欄位，只有本地 HMI 角色登入，語意不同不宜混用)、1513 Tester On/Off(本機為 Tray Sorter，無測試機)。
+剩下 2 格中，1007 Operator ID 已於同日「追加項3」實作(見本表末)，⚠ 本項原先建議貴端自報表定義中移除 1007，該建議作廢，請保留。真正給不出來的只有 1513 Tester On/Off(本機為 Tray Sorter，無測試機)，建議自報表定義中移除。
 同一封信的另一張截圖 RPTID 501 = {1101, 1102, 1103-1108, 16296-16299} 全空，本版起 12 格中有 5 格有值(1101 Loader Count、1102 Output Total、1103-1105 Auto1-3)；其餘見第 4、5 項。</t>
         </is>
       </c>
@@ -1469,8 +1471,8 @@
       <c r="B60" s="40" t="inlineStr">
         <is>
           <t>本版完全依此原則：凡 HT9045 已有同概念的資料，一律沿用 HT9045 的號碼、型別與線上格式(上列 13 個號碼即是)；只有 HT9045 沒有的功能才放在本機自有、HT9045 未使用的高位段。
-唯一需要貴端裁定的是輸出站計數：HT9045 只給三個 Auto 編號(1103-1105)，第 4/5/6 站在 HT9045 叫 Fix1-3(1106-1108)，而 HT-160S 是六個 Auto、沒有 Fix 站。把 Auto4-6 對映到 1106-1108 屬雙方商務決定，本機不單方面認定，因此 RPTID 501 的第 6-8 格維持空 item。
-但 Auto4-6 的產出並未隱藏：這三站公佈於本機自有的 66025-66027(HT9045 無對應號碼)，貴端以 S2F33 綁該段即可讀到。六站完整分布 = 1103 / 1104 / 1105 + 66025 / 66026 / 66027。若貴端確認 Fix1-3 即為第 4/5/6 輸出站，本機可改以 1106-1108 回報(一行設定，不需改機構)。</t>
+唯一需要貴端裁定的是輸出站計數：HT-9046LS(貴端機型)只給三個 Auto 編號(1103-1105)，第 4/5/6 站在該機型叫 Fix1-3(1106-1108)，而 HT-160S 是六個 Auto、沒有 Fix 站。把 Auto4-6 對映到 1106-1108 屬雙方商務決定，本機不單方面認定，因此 RPTID 501 的第 6-8 格維持空 item。
+但 Auto4-6 的產出並未隱藏，且自同日「追加項5」起也已使用 HT9045 家族編號：HT9045 家族中的 HT-9011UC V3.33.899 本身就是六站 Auto 機台，以 1259 / 1260 / 1261 命名 Auto4-6 Count(其後 1262 起為 Fix 7-12)，故本機改用該組號碼，不再使用自有段 66025-66027。六站完整分布 = 1103 / 1104 / 1105 + 1259 / 1260 / 1261。若貴端另確認 Fix1-3 即為第 4/5/6 輸出站，本機可改以 1106-1108 回報並同時下架 1259-1261(一行設定，不需改機構)—— 是「改用」而非「多加一組」，仍維持一個資料一個編號的原則。</t>
         </is>
       </c>
     </row>
@@ -1631,6 +1633,7 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="38" t="inlineStr">
         <is>
@@ -1662,7 +1665,7 @@
           <t>依貴端 2026-08-03 來信第 3 點「相同功能用同一編號」的原則，本機自有段中四個與 HT9045 號碼同值、同來源的號碼予以移除。⚠ 這是本次唯一需要貴端調整設定的變更：
 • 移除 SVID 66022 / 66023 / 66024 Auto1-3 Count —— 與 1103 / 1104 / 1105 指向機台內同一組計數器，數值恆等，並非兩份資料。請改讀 1103 / 1104 / 1105。
 • 移除 SVID 66033 Lot Start Time —— 與 1009 為同一個閂鎖、同一時刻，僅分隔符不同(66033 為斜線 'yyyy/mm/dd hh:nn:ss'，1009 為 HT9045 線上格式 'yyyy-mm-dd hh:nn:ss')。請改讀 1009。原 66033 的全部行為由 1009 完整承接:Lot Start 閂鎖(面板按鈕與 SECS LOTSTART 兩條路徑)、Lot End 清空、跨電源「沿用工單」時以原始開批時刻回填、未加入預設 Report 1。
-• 保留 SVID 66025 / 66026 / 66027 Auto4-6 Count —— HT9045 無對應號碼(其第 4-6 站叫 Fix1-3)，故仍留在本機自有段，號碼不變、不遞補、不重新編號。六站完整分布 = 1103 / 1104 / 1105 + 66025 / 66026 / 66027。
+• SVID 66025 / 66026 / 66027 Auto4-6 Count —— 見「追加項5」:已改用 HT-9011UC V3.33.899 的家族編號 1259 / 1260 / 1261，本機自有段自此不再公佈任何 per-Auto 產出計數。六站完整分布 = 1103 / 1104 / 1105 + 1259 / 1260 / 1261。
 • 被移除的四個號碼保留空號，永不挪作他用。貴端設定若未更新，S1F3 與報表中該欄位會回空 item(未知 SVID)，報表長度不變、不會位移到別的資料上，故不存在靜默誤讀的風險 —— 但該欄位將永遠為空，請務必改綁。
 註:同樣「一資料兩編號」的還有 66021 Total Sorted / 1102 Output Total Count 與 66002 Control State / SVID 4 GemControlState，本次刻意不動:66021 與 66002 都在預設 Report 1 的 13 個 SV 之內，移除會改變線上每一筆事件的長度與欄位順序;66002 另與 SVID 4 值域不同(GEM 標準 1/4/5 對 HT9045 的 1/2/3)，並非可直接互換的別名。</t>
         </is>
@@ -1702,9 +1705,270 @@
         <is>
           <t>1. 建置:模擬版 -Full、真機版(註銷 SOFT_SIMULATE)-Full、還原後再 -Full,三次建置皆 exit 0,原始碼編碼檢查通過。
 2. 以 headless SECS host 對實際韌體(EXE\ht160s.exe)做 HSMS round-trip 實測(2026-08-03 10:22-10:24):
-• 單一 S1F3 同時查 14 個號碼:66022 / 66023 / 66024 / 66033 四格全部回空 item(未知 SVID);1103 = 1、1104 = 1、1105 = 1、66025 = 1、66026 = 0、66027 = 0 皆為真值,1102、66021、1001 亦正常。⚠ 回覆的 L 長度為 14,與請求的 14 個號碼完全一致 —— 實測證實移除號碼不會改變報表長度、後續欄位不會位移,設定未更新的 host 只會看到該格為空,不會誤讀到別的資料。
+• 單一 S1F3 同時查 14 個號碼:66022 / 66023 / 66024 / 66033 四格全部回空 item(未知 SVID);1103 = 1、1104 = 1、1105 = 1、66025 = 1、66026 = 0、66027 = 0 皆為真值〔註:66025-66027 已於同日「追加項5」改號為 1259-1261;此處為當時的實測記錄，不予追改〕,1102、66021、1001 亦正常。⚠ 回覆的 L 長度為 14,與請求的 14 個號碼完全一致 —— 實測證實移除號碼不會改變報表長度、後續欄位不會位移,設定未更新的 host 只會看到該格為空,不會誤讀到別的資料。
 • 再送 SET_LOT_INFO 與 LOTSTART(兩者 HCACK 皆為 0)後重查:SVID 1009 由空字串變為 '2026-08-03 10:24:24',而同一次回覆中的 SVID 1027 System Time 為 '2026/08/03 10:24:26' —— 兩者相差 2 秒,證實 1009 取的是開批當下的閂鎖值而非跟著系統時鐘走;66033 在開批後仍為空,證實該號碼確已下架、且開批時刻的閂鎖與持久化機制未受影響。
 3. 上機驗證待執行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="38" t="inlineStr">
+        <is>
+          <t>2026-08-03 第 4 版 追加項3(同日，承追加項2)</t>
+        </is>
+      </c>
+      <c r="B83" s="40" t="n"/>
+    </row>
+    <row r="84" ht="33" customHeight="1" s="8">
+      <c r="A84" s="38" t="inlineStr">
+        <is>
+          <t>依據韌體 Firmware</t>
+        </is>
+      </c>
+      <c r="B84" s="40" t="inlineStr">
+        <is>
+          <t>HT-160S 1.0.0.0, branch feat/iosetview-172-refactor (CEID 字典補齊至 292 + CEID 272-275 名稱更正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="231" customHeight="1" s="8">
+      <c r="A85" s="38" t="inlineStr">
+        <is>
+          <t>10. CEID 字典已依貴端現場機台逐筆核對，並補齊至 292</t>
+        </is>
+      </c>
+      <c r="B85" s="40" t="inlineStr">
+        <is>
+          <t>資料來源不是原始碼，而是貴端 HT-9046 現場機台自己存下來的 EventReport_CEID.def(2026-06-25)。逐筆比對結果:
+• CEID 1-275 與本機完全相同，0 筆別名不符 —— 證實本機的 CEID 編號與語意，就是貴端 host 當初設定所依據的那一套。這是本次核對最重要的結論。
+• 貴端機台另有 276-292 共 17 個號碼是本機先前沒有的:276 Loader_Buffer_NoTray、277-282 OutputPort1-6BinCode、283 MaterialModeChange、284 PortStateUpdated、285 UnloaderTrayIDReadOK、286 UnloaderTrayIDReadFail、287 LoaderTrayIDReadFail、288 MaximumOutputPortReport、289 RunCheckRequest、290 AGVLDUnLDFinish、291 AGVLdID、292 DoSecsGemIndexFail。本版已全部註冊(名稱逐字照抄該檔)，使兩機字典完全一致。
+• 這 17 個目前只有註冊、沒有發射點。其中 277-282(各 Auto 出料站 Bin code)、285/286/287(Tray ID 讀取結果)、276(Loader 緩衝無盤)本機機構上做得到，若貴端需要，請提供貴端機台這幾個事件的實際 S6F11 範例(要帶哪些 SVID)，本機即可比照實作。
+• 影響:S1F23/S1F24 全查的回覆由 L,275 變為 L,292(約 32 KB)。此訊息為字典查詢，不等於訂閱 —— 要收哪些事件仍由 S2F33 / S2F35 / S2F37 決定，故對既有事件流量與內容毫無影響。
+⚠ 給雙方工程人員的提醒:HT-90XX 另有一條 HT9011UC(V3.33.9xx)分支，它把 CEID 217-271 整段重新編號(該分支的 217 是 LoadPortStatusChanged，貴端機台與本機都是 Reserved_06)，並把上述 sorter 事件放在 275-288 而非 276-292。貴端機台用的不是那一套。日後任何一方要更新字典，請以貴端機台的 .def 或本規格書為準，不要從 HT9011UC 分支同步，否則 55 個號碼會靜默變義。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="132" customHeight="1" s="8">
+      <c r="A86" s="38" t="inlineStr">
+        <is>
+          <t>11. 更正 CEID 272-275 的名稱(僅名稱字串，號碼與行為不變)</t>
+        </is>
+      </c>
+      <c r="B86" s="40" t="inlineStr">
+        <is>
+          <t>同一次核對發現本機 S1F24 對 CEID 272/273/274/275 回的 CENAME 是本機自用字串 AGVSupplement / AGVLDUnLDStatus / AGVLDUnLDFinish / AGVLdID，與貴端機台的 AMR Supplement / AMR LDUnLD Status / AMR LDUnLD Finish / AMR LD ID 不一致。成因是本機在改綁 AMR 專屬報表時，用字面字串覆寫了原本已對齊的別名，而這四個正好是貴端唯一實際使用的 AMR 事件。本版已改為與貴端機台一致。⚠ CEID 號碼、攜帶報表、發射時機完全未變，只有 S1F24 回覆的名稱字串改了 —— 以號碼設定者(一般作法)不受影響;以名稱比對者請以本版為準。除這四個之外，1-292 的其餘號碼在核對前就已全部一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="82.5" customHeight="1" s="8">
+      <c r="A87" s="38" t="inlineStr">
+        <is>
+          <t>本次未變動 Unchanged</t>
+        </is>
+      </c>
+      <c r="B87" s="40" t="inlineStr">
+        <is>
+          <t>所有事件的發射時機、攜帶報表、酬載內容與線上形狀完全不變。本追加項3 只做兩件事:把字典補齊到與貴端機台相同的 292 個號碼，以及更正四個號碼的名稱字串。有發射點的號碼仍為 57 個(56 個無條件 + CEID 78 條件發射)，新增的 17 個全部沒有發射點。SVID 表亦不變(仍為追加項2 之後的 75 個)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="99" customHeight="1" s="8">
+      <c r="A88" s="38" t="inlineStr">
+        <is>
+          <t>追加項3 的驗證 Verification</t>
+        </is>
+      </c>
+      <c r="B88" s="40" t="inlineStr">
+        <is>
+          <t>1. 建置:模擬版 -Full、真機版(註銷 SOFT_SIMULATE)-Full、還原後再 -Full，三次建置皆 exit 0;原始碼編碼檢查 166 檔通過，警報碼登錄檢查通過。
+2. 以 headless SECS host 對實際韌體(EXE\ht160s.exe)實測 S1F23 &lt;L[0]&gt; 全查:回 L,292、32,112 bytes，並將回覆中的 292 筆 CENAME 與貴端機台的 EventReport_CEID.def 逐筆自動比對 —— 0 筆不符。修正前的同一支測試在 272/273/274/275 上報 4 筆不符，即上述第 11 項的缺陷，修正後歸零。
+3. 上機驗證待執行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" s="38" t="inlineStr">
+        <is>
+          <t>2026-08-03 第 4 版 追加項4(同日，承追加項3)</t>
+        </is>
+      </c>
+      <c r="B90" s="40" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="38" t="inlineStr">
+        <is>
+          <t>依據韌體 Firmware</t>
+        </is>
+      </c>
+      <c r="B91" s="40" t="inlineStr">
+        <is>
+          <t>HT-160S 1.0.0.0, branch feat/iosetview-172-refactor (SVID/ECID 1007 Operator ID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="38" t="inlineStr">
+        <is>
+          <t>13. 新增 SVID / ECID 1007 Operator ID(回應來信第 3 點，並更正第 4 版第 3 項的建議)</t>
+        </is>
+      </c>
+      <c r="B92" s="40" t="inlineStr">
+        <is>
+          <t>本機新增操作員身分欄位，號碼、型別與可寫性皆比照 HT-90XX：
+• 主畫面右側設定區新增「Operator ID」輸入欄，預設值 "Operator"，觸控點擊叫出螢幕鍵盤;輸入後存入 General.ini [MachineIdentity] OperatorID，跨電源保存。
+• 以 SVID 1007(A，ASCII)公佈，可由 S1F3 隨時回查，並填入貴端 RPTID 502 的第 2 格。
+• 同時以 ECID 1007 註冊，⚠ 本機接受貴端以 S2F15 寫入 —— 這是 HT9045 的作法(其 ECID 1007 綁在 fLotInfo 的 Operator ID 欄位)，也是貴端 2026-06-08 現場 log 中的實際用法:當天 24 筆 S2F15 中有 4 筆寫 ECID 1007 = "AGV"。寫入成功回 EAC=0，值會即時顯示在主畫面該欄位、寫入 General.ini 保存，並發 CEID 48 Change EC。空字串一律拒絕(EAC=3)，確保本欄永不回空 item。
+• ⚠ 與其他可寫 EC 不同，1007 在機台運轉中也接受寫入(不會回 EAC=2)。理由:其餘可寫的 2758-2763 是 Tray 幾何，運轉中變更會位移取放座標，故以運轉狀態為閘;1007 只是識別字串，無機構後果，而貴端正是在運轉當下寫它，若比照設閘則每一筆都會被拒。
+• 語意界定:1007 是「本班作業人員身分」，由貴端 host 或現場人員填寫。本機另有的 HMI 角色登入(Operation / Supervisor / Engineer / Honprec)屬本地權限控制，會因技術員中途登入而改變，語意不同，刻意不與 1007 綁定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="38" t="inlineStr">
+        <is>
+          <t>14. RPTID 502 覆蓋率更新，並更正第 4 版第 3 項</t>
+        </is>
+      </c>
+      <c r="B93" s="40" t="inlineStr">
+        <is>
+          <t>502 = {1006, 1007, 1011, 3, 1501, 1517, 1518, 1513} 共 8 格，本追加項後 7 格有值(前版 6 格)。
+⚠ 第 4 版第 3 項原建議「貴端自報表定義中移除 1007 Operator ID(本機無操作員身分欄位)」，該建議即日作廢 —— 1007 已實作，請保留在報表定義中。該處敘述已一併更正。
+仍建議移除的只剩 1513 Tester On/Off:本機為 Tray Sorter，無測試機，機構上給不出來。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="38" t="inlineStr">
+        <is>
+          <t>15. SVID 表</t>
+        </is>
+      </c>
+      <c r="B94" s="40" t="inlineStr">
+        <is>
+          <t>新增 1007 Operator ID 一列。本機共註冊 76 個 SVID(追加項2 後為 75)。1007 同時存在於 EC 命名空間(可讀可寫)，與 1501 / 2758-2763 的雙註冊作法一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="38" t="inlineStr">
+        <is>
+          <t>本次未變動 Unchanged</t>
+        </is>
+      </c>
+      <c r="B95" s="40" t="inlineStr">
+        <is>
+          <t>CEID 的編號、語意與發射點(含追加項3 的字典補齊結果)、預設 Report 1 的 13 個 SV 內容與順序、S1F23/S1F24 與 S2F29/S2F30 的回覆形狀、S5 警報目錄、Soter 輸出檔契約。EC 可寫範圍本次「擴大」一個號碼(1007)，除此之外未變動;1007 未加入預設 Report 1，故既有事件的線上形狀完全不變。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="38" t="inlineStr">
+        <is>
+          <t>追加項4 的驗證 Verification</t>
+        </is>
+      </c>
+      <c r="B96" s="40" t="inlineStr">
+        <is>
+          <t>1. 建置:模擬版建置 exit 0;註銷 SOFT_SIMULATE 之真機版建置 exit 0;還原 SOFT_SIMULATE 後全部編譯單元再次編譯通過。原始碼編碼檢查 166 檔通過，表單 __published 形狀檢查 60 檔通過。
+2. ⚠ 尚未進行 HSMS round-trip 實測(S1F3 讀 1007 / S2F15 寫 1007 → EAC 與 CEID 48 / S2F13 讀 EC 1007)，亦尚未上機驗證主畫面欄位與螢幕鍵盤。此兩項完成前，本項應視為「已實作、待驗證」，與本表其餘各項(皆已完成 round-trip 實測)的成熟度不同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="38" t="n"/>
+      <c r="B97" s="40" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="38" t="inlineStr">
+        <is>
+          <t>2026-08-03 第 4 版 追加項5(同日，承追加項4)</t>
+        </is>
+      </c>
+      <c r="B98" s="40" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="38" t="inlineStr">
+        <is>
+          <t>依據韌體 Firmware</t>
+        </is>
+      </c>
+      <c r="B99" s="40" t="inlineStr">
+        <is>
+          <t>HT-160S 1.0.0.0, branch feat/iosetview-172-refactor (Auto4-6 對齊家族編號:Count 1259-1261、Carrier ID 38199-38201)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="38" t="inlineStr">
+        <is>
+          <t>⚠ 16. Auto4-6 Count 改用 HT9045 家族編號 1259 / 1260 / 1261(此項為 breaking change)</t>
+        </is>
+      </c>
+      <c r="B100" s="40" t="inlineStr">
+        <is>
+          <t>本機自有段的 66025 / 66026 / 66027 Auto4-6 Count 原本以「HT9045 無對應號碼」為理由存在(見第 4 版第 4 項與追加項2 第 8 項)。該理由已被推翻:HT9045 家族中的 HT-9011UC V3.33.899 本身就是六站 Auto 機台，其 SVID 目錄以 1259 = Auto 4 Count、1260 = Auto 5 Count、1261 = Auto 6 Count 命名(其後 1262 起為 Fix 7-12)。依貴端「相同功能使用同一編號」的原則，本機自本版起改用 1259 / 1260 / 1261。
+• 移除 SVID 66025 / 66026 / 66027，新增 SVID 1259 / 1260 / 1261。型別(I4)、單位(pcs)、資料來源(各 Auto 出料盤的放料計數器)與累加時機完全不變，只換編號。
+• ⚠ 若貴端已在 S2F33 報表定義或 S1F3 輪詢中綁定 66025-66027，請改綁 1259 / 1260 / 1261;未更新前該三格會回空 item(未知 SVID)。與追加項2 相同，報表長度不變、欄位不會位移到別的資料上，不存在靜默誤讀的風險，但該欄位將永遠為空。
+• 六站完整分布 = 1103 / 1104 / 1105 + 1259 / 1260 / 1261 —— 六站全部使用 HT9045 家族編號，本機自有段不再公佈任何 per-Auto 產出計數。
+• 這與 Fix1-3(1106-1108)是兩件不同的事:HT-9046LS(貴端機型)把第 4-6 個出料站叫 Fix1-3，要不要把 HT-160S 的 Auto4-6 對映到 1106-1108 仍屬雙方商務決定，本機不單方面認定，RPTID 501 的第 6-8 格維持空 item。若日後貴端確認，做法是**改用** 1106-1108 並同時下架 1259-1261，不會兩組並存(維持一個資料一個編號)。
+• 66022-66027 這六個空號永不遞補、永不改用他義。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="38" t="inlineStr">
+        <is>
+          <t>17. SVID 表</t>
+        </is>
+      </c>
+      <c r="B101" s="40" t="inlineStr">
+        <is>
+          <t>移除 66025、66026、66027 三列，新增 1259、1260、1261 三列;另移除 38208、38209、38210 三列，新增 38199、38200、38201 三列(見第 18 項)。本機共註冊 76 個 SVID(數量不變:兩批各減 3 加 3;追加項4 後為 76)。SVID 表(本檔第 3 個工作表)一律以當下實際註冊內容為準。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="38" t="inlineStr">
+        <is>
+          <t>⚠ 18. Auto4-6 的 AMR Carrier ID 改用家族編號 38199 / 38200 / 38201(此項為 breaking change)</t>
+        </is>
+      </c>
+      <c r="B102" s="40" t="inlineStr">
+        <is>
+          <t>同一條原則(Auto1-3 遵循 HT-9046LS V3.32.810、Auto4-6 參照 HT-9011UC V3.33.899)套用到 AMR 盤號欄位:
+• Auto1-3 Carrier ID 維持 38205 / 38206 / 38207 —— 810 的 SVID 定義(uHGemHT9045_SV.cpp:797-799)，不變。
+• Auto4-6 Carrier ID 由本機自創的 38208 / 38209 / 38210 改為 899 的 38199 / 38200 / 38201(名稱 Output 4/5/6 Tray ID，uHGemHT9045_EC.cpp:1664-1666)。⚠ 若貴端已綁定 38208-38210，請改綁 38199-38201;舊號碼即日起為空號，永不改用他義。
+• 命名空間說明:899 把整個盤號家族(含其自身的 38205-38207)宣告在 ECID;本機維持 SVID，因為 Auto1-3 是照 810 的 SVID 定義，六個出料口必須在同一個命名空間回答。
+• Auto4-6 的 tray / device / bin-setting(38237-38245)維持本機延伸號不變 —— 已逐檔查證兩棵參照樹皆無可對齊的號碼:810 的 AMR 段是 38222-38236 且止於 38236，HT-9011UC V3.33.899 整段沒有 AMR SVID 家族。這同時結掉第 4 版「需向貴端索取 9045 SVID 目錄才能判定」那條待確認事項。
+• 影響面:CEID 272 / 273 / 274 / 275 的 AMR 報表中，P7-P9 的 carrier 欄位編號改變(欄位數量、順序、酬載型別皆不變)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="38" t="inlineStr">
+        <is>
+          <t>本次未變動 Unchanged</t>
+        </is>
+      </c>
+      <c r="B103" s="40" t="inlineStr">
+        <is>
+          <t>CEID 的編號、語意與發射點、預設 Report 1 的 13 個 SV 內容與順序、S1F23/S1F24 與 S2F29/S2F30 的回覆形狀、EC 可寫範圍、S5 警報目錄、Soter 輸出檔契約。被移除的 66025-66027 從未納入預設 Report 1，故既有事件的線上形狀完全不變;38199-38201 取代 38208-38210 後，AMR 報表(CEID 272/273/274/275)的欄位數量、順序與型別亦完全不變，只有 P7-P9 carrier 的編號改變。機台的計數與盤號行為、數值皆完全不變 —— 本次只更換對外公佈的編號。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="38" t="inlineStr">
+        <is>
+          <t>追加項5 的驗證 Verification</t>
+        </is>
+      </c>
+      <c r="B104" s="40" t="inlineStr">
+        <is>
+          <t>1. 建置:模擬版 -Full exit 0;註銷 SOFT_SIMULATE 之真機版 -Full exit 0;還原 SOFT_SIMULATE 後再次 -Full exit 0。
+2. 號碼衝突已逐一查證:(a) HT-9046LS V3.32.810 完全未定義 1256-1262，HT-9011UC V3.33.899 的 1259-1261 即為 Auto 4-6 Count，本機先前亦未使用這三個號碼;(b) 810 在 38195-38201 區間未定義任何號碼(其段為 38202、38205-38207、38219 起)，本機先前亦未使用 38199-38201 —— 兩批六個新號碼三方皆無衝突。
+3. ⚠ 尚未進行 HSMS round-trip 實測(預期:S1F3 讀 1259 / 1260 / 1261 與 38199 / 38200 / 38201 回真值，讀 66025 / 66026 / 66027 與 38208 / 38209 / 38210 回空 item)，亦尚未上機驗證 AMR 報表。此兩項於下一批次補做。</t>
         </is>
       </c>
     </row>
@@ -1952,7 +2216,7 @@
   &lt;L [0] 
   &gt;
 .
-[20260730] 已實作(2026-07-30 新增)。S1F23 -&gt; S1F24 回 L,n{L,3{U4 CEID, A CENAME, L,m{U4 VID}}}。&lt;L[0]&gt; 全查回全部 275 個 CEID(與 HT9045 字典逐字相同，含本機已註冊但不發射的 223 個)；指定 CEID 只回該幾筆；未註冊的 CEID 回 {CEID, '', L,0}(與 HT9045 同)。VID 清單由該 CEID 所連結的報表依序展開，順序與該事件 S6F11 內的排列一致，重複的 VID 不去除(一個 CEID 連兩張含相同 SVID 的報表時，S6F11 本來就會送兩次)。註：本訊息只是字典查詢，不等於訂閱 — 實際要收哪些事件仍由 S2F33 / S2F35 / S2F37 決定。</t>
+[20260730] 已實作(2026-07-30 新增)。S1F23 -&gt; S1F24 回 L,n{L,3{U4 CEID, A CENAME, L,m{U4 VID}}}。&lt;L[0]&gt; 全查回全部 292 個 CEID(與貴端現場機台的字典逐筆相同，含本機已註冊但不發射的 235 個)〔20260803:由 275 補齊為 292，見「第 4 版 追加項3」〕；指定 CEID 只回該幾筆；未註冊的 CEID 回 {CEID, '', L,0}(與 HT9045 同)。VID 清單由該 CEID 所連結的報表依序展開，順序與該事件 S6F11 內的排列一致，重複的 VID 不去除(一個 CEID 連兩張含相同 SVID 的報表時，S6F11 本來就會送兩次)。註：本訊息只是字典查詢，不等於訂閱 — 實際要收哪些事件仍由 S2F33 / S2F35 / S2F37 決定。</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="6.5" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -3242,680 +3506,690 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="n">
+      <c r="A9" s="54" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>Operator ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="51" t="n">
         <v>1009</v>
       </c>
-      <c r="B9" s="51" t="inlineStr">
+      <c r="B10" s="51" t="inlineStr">
         <is>
           <t>Lot Start Time</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="54" t="n">
+    <row r="11">
+      <c r="A11" s="54" t="n">
         <v>1011</v>
       </c>
-      <c r="B10" s="54" t="inlineStr">
+      <c r="B11" s="54" t="inlineStr">
         <is>
           <t>Machine State</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>1021</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>UPH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>UPH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
         <v>1027</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>System Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="54" t="n">
-        <v>1101</v>
-      </c>
-      <c r="B13" s="54" t="inlineStr">
-        <is>
-          <t>Loader Count</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="54" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>Loader Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="54" t="n">
         <v>1102</v>
       </c>
-      <c r="B14" s="54" t="inlineStr">
+      <c r="B15" s="54" t="inlineStr">
         <is>
           <t>Output Total Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="51" t="n">
-        <v>1103</v>
-      </c>
-      <c r="B15" s="51" t="inlineStr">
-        <is>
-          <t>Auto1 Count</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="51" t="n">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B16" s="51" t="inlineStr">
         <is>
-          <t>Auto2 Count</t>
+          <t>Auto1 Count</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="51" t="n">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B17" s="51" t="inlineStr">
         <is>
-          <t>Auto3 Count</t>
+          <t>Auto2 Count</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="51" t="n">
-        <v>1501</v>
+        <v>1105</v>
       </c>
       <c r="B18" s="51" t="inlineStr">
         <is>
-          <t>Setup File</t>
+          <t>Auto3 Count</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="54" t="n">
-        <v>1517</v>
-      </c>
-      <c r="B19" s="54" t="inlineStr">
-        <is>
-          <t>Start Mode</t>
+      <c r="A19" s="51" t="n">
+        <v>1259</v>
+      </c>
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t>Auto4 Count</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="n">
-        <v>1518</v>
-      </c>
-      <c r="B20" s="53" t="inlineStr">
-        <is>
-          <t>Real/Dummy</t>
+      <c r="A20" s="54" t="n">
+        <v>1260</v>
+      </c>
+      <c r="B20" s="54" t="inlineStr">
+        <is>
+          <t>Auto5 Count</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="51" t="n">
-        <v>2758</v>
-      </c>
-      <c r="B21" s="51" t="inlineStr">
-        <is>
-          <t>Type 1 Tray Pitch X</t>
+      <c r="A21" s="53" t="n">
+        <v>1261</v>
+      </c>
+      <c r="B21" s="53" t="inlineStr">
+        <is>
+          <t>Auto6 Count</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="51" t="n">
-        <v>2759</v>
+        <v>1501</v>
       </c>
       <c r="B22" s="51" t="inlineStr">
         <is>
-          <t>Type 1 Tray Pitch Y</t>
+          <t>Setup File</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="51" t="n">
-        <v>2760</v>
+        <v>1517</v>
       </c>
       <c r="B23" s="51" t="inlineStr">
         <is>
-          <t>Type 1 Tray Start Position X</t>
+          <t>Start Mode</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="51" t="n">
-        <v>2761</v>
+        <v>1518</v>
       </c>
       <c r="B24" s="51" t="inlineStr">
         <is>
-          <t>Type 1 Tray Start Position Y</t>
+          <t>Real/Dummy</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="51" t="n">
-        <v>2762</v>
+        <v>2758</v>
       </c>
       <c r="B25" s="51" t="inlineStr">
         <is>
-          <t>Type 1 Tray Division X</t>
+          <t>Type 1 Tray Pitch X</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="51" t="n">
-        <v>2763</v>
+        <v>2759</v>
       </c>
       <c r="B26" s="51" t="inlineStr">
         <is>
-          <t>Type 1 Tray Division Y</t>
+          <t>Type 1 Tray Pitch Y</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="54" t="n">
-        <v>37010</v>
-      </c>
-      <c r="B27" s="54" t="inlineStr">
-        <is>
-          <t>Enter Skip IC Count</t>
+      <c r="A27" s="51" t="n">
+        <v>2760</v>
+      </c>
+      <c r="B27" s="51" t="inlineStr">
+        <is>
+          <t>Type 1 Tray Start Position X</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>38202</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Loader Carrier ID</t>
+      <c r="A28" s="54" t="n">
+        <v>2761</v>
+      </c>
+      <c r="B28" s="54" t="inlineStr">
+        <is>
+          <t>Type 1 Tray Start Position Y</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>38203</v>
+        <v>2762</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Empty Carrier ID</t>
+          <t>Type 1 Tray Division X</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>38204</v>
+        <v>2763</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Color Carrier ID</t>
+          <t>Type 1 Tray Division Y</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>38205</v>
+        <v>37010</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>AUTO1 Carrier ID</t>
+          <t>Enter Skip IC Count</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>38206</v>
+        <v>38199</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>AUTO2 Carrier ID</t>
+          <t>AUTO4 Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>38207</v>
+        <v>38200</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>AUTO3 Carrier ID</t>
+          <t>AUTO5 Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>38208</v>
+        <v>38201</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>AUTO4 Carrier ID</t>
+          <t>AUTO6 Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>38209</v>
+        <v>38202</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>AUTO5 Carrier ID</t>
+          <t>Loader Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>38210</v>
+        <v>38203</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>AUTO6 Carrier ID</t>
+          <t>Empty Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>38219</v>
+        <v>38204</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Supplement Bin</t>
+          <t>Color Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>38220</v>
+        <v>38205</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>LD UnLD Check AGV</t>
+          <t>AUTO1 Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>38221</v>
+        <v>38206</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>LD UnLD Finish AGV</t>
+          <t>AUTO2 Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="34" t="n">
-        <v>38222</v>
-      </c>
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>AMR Loader Tray Count</t>
+      <c r="A40" s="7" t="n">
+        <v>38207</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>AUTO3 Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>38223</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>AMR Empty Tray Count</t>
+      <c r="A41" s="34" t="n">
+        <v>38219</v>
+      </c>
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>Supplement Bin</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>38224</v>
+        <v>38220</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>AMR Color Tray Count</t>
+          <t>LD UnLD Check AGV</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>38225</v>
+        <v>38221</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>AMR AUTO1 Tray Count</t>
+          <t>LD UnLD Finish AGV</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>38226</v>
+        <v>38222</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>AMR AUTO2 Tray Count</t>
+          <t>AMR Loader Tray Count</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>38227</v>
+        <v>38223</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>AMR AUTO3 Tray Count</t>
+          <t>AMR Empty Tray Count</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>38228</v>
+        <v>38224</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>AMR Loader Device Count</t>
+          <t>AMR Color Tray Count</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>38229</v>
+        <v>38225</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>AMR Empty Device Count</t>
+          <t>AMR AUTO1 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>38230</v>
+        <v>38226</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>AMR Color Device Count</t>
+          <t>AMR AUTO2 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>38231</v>
+        <v>38227</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>AMR AUTO1 Device Count</t>
+          <t>AMR AUTO3 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>38232</v>
+        <v>38228</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>AMR AUTO2 Device Count</t>
+          <t>AMR Loader Device Count</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>38233</v>
+        <v>38229</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>AMR AUTO3 Device Count</t>
+          <t>AMR Empty Device Count</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="52" t="n">
-        <v>38234</v>
-      </c>
-      <c r="B52" s="55" t="inlineStr">
-        <is>
-          <t>AMR AUTO1 Bin Setting</t>
+      <c r="A52" s="7" t="n">
+        <v>38230</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>AMR Color Device Count</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="52" t="n">
-        <v>38235</v>
+        <v>38231</v>
       </c>
       <c r="B53" s="55" t="inlineStr">
         <is>
-          <t>AMR AUTO2 Bin Setting</t>
+          <t>AMR AUTO1 Device Count</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="52" t="n">
-        <v>38236</v>
+        <v>38232</v>
       </c>
       <c r="B54" s="55" t="inlineStr">
         <is>
-          <t>AMR AUTO3 Bin Setting</t>
+          <t>AMR AUTO2 Device Count</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="52" t="n">
-        <v>38237</v>
+        <v>38233</v>
       </c>
       <c r="B55" s="55" t="inlineStr">
         <is>
-          <t>AMR AUTO4 Tray Count</t>
+          <t>AMR AUTO3 Device Count</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="52" t="n">
-        <v>38238</v>
+        <v>38234</v>
       </c>
       <c r="B56" s="55" t="inlineStr">
         <is>
-          <t>AMR AUTO5 Tray Count</t>
+          <t>AMR AUTO1 Bin Setting</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="52" t="n">
-        <v>38239</v>
+        <v>38235</v>
       </c>
       <c r="B57" s="55" t="inlineStr">
         <is>
-          <t>AMR AUTO6 Tray Count</t>
+          <t>AMR AUTO2 Bin Setting</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="52" t="n">
-        <v>38240</v>
+        <v>38236</v>
       </c>
       <c r="B58" s="55" t="inlineStr">
         <is>
-          <t>AMR AUTO4 Device Count</t>
+          <t>AMR AUTO3 Bin Setting</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="52" t="n">
-        <v>38241</v>
+        <v>38237</v>
       </c>
       <c r="B59" s="55" t="inlineStr">
         <is>
-          <t>AMR AUTO5 Device Count</t>
+          <t>AMR AUTO4 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="52" t="n">
-        <v>38242</v>
+        <v>38238</v>
       </c>
       <c r="B60" s="55" t="inlineStr">
         <is>
-          <t>AMR AUTO6 Device Count</t>
+          <t>AMR AUTO5 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="52" t="n">
-        <v>38243</v>
+        <v>38239</v>
       </c>
       <c r="B61" s="55" t="inlineStr">
         <is>
-          <t>AMR AUTO4 Bin Setting</t>
+          <t>AMR AUTO6 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="52" t="n">
-        <v>38244</v>
+        <v>38240</v>
       </c>
       <c r="B62" s="55" t="inlineStr">
         <is>
-          <t>AMR AUTO5 Bin Setting</t>
+          <t>AMR AUTO4 Device Count</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="52" t="n">
-        <v>38245</v>
+        <v>38241</v>
       </c>
       <c r="B63" s="55" t="inlineStr">
         <is>
-          <t>AMR AUTO6 Bin Setting</t>
+          <t>AMR AUTO5 Device Count</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="52" t="n">
-        <v>66000</v>
+        <v>38242</v>
       </c>
       <c r="B64" s="55" t="inlineStr">
         <is>
-          <t>Run Mode</t>
+          <t>AMR AUTO6 Device Count</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="52" t="n">
-        <v>66001</v>
+        <v>38243</v>
       </c>
       <c r="B65" s="55" t="inlineStr">
         <is>
-          <t>System Running</t>
+          <t>AMR AUTO4 Bin Setting</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="52" t="n">
-        <v>66002</v>
+        <v>38244</v>
       </c>
       <c r="B66" s="55" t="inlineStr">
         <is>
-          <t>Control State</t>
+          <t>AMR AUTO5 Bin Setting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="52" t="n">
-        <v>66010</v>
+        <v>38245</v>
       </c>
       <c r="B67" s="55" t="inlineStr">
         <is>
-          <t>Alarm Active</t>
+          <t>AMR AUTO6 Bin Setting</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="52" t="n">
-        <v>66011</v>
+        <v>66000</v>
       </c>
       <c r="B68" s="55" t="inlineStr">
         <is>
-          <t>Alarm Code</t>
+          <t>Run Mode</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="52" t="n">
-        <v>66020</v>
+        <v>66001</v>
       </c>
       <c r="B69" s="55" t="inlineStr">
         <is>
-          <t>Total IC</t>
+          <t>System Running</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="52" t="n">
-        <v>66021</v>
+        <v>66002</v>
       </c>
       <c r="B70" s="55" t="inlineStr">
         <is>
-          <t>Total Sorted</t>
+          <t>Control State</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="38" t="n">
-        <v>66025</v>
-      </c>
-      <c r="B71" s="38" t="inlineStr">
-        <is>
-          <t>Auto4 Count</t>
+      <c r="A71" s="52" t="n">
+        <v>66010</v>
+      </c>
+      <c r="B71" s="55" t="inlineStr">
+        <is>
+          <t>Alarm Active</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="38" t="n">
-        <v>66026</v>
+        <v>66011</v>
       </c>
       <c r="B72" s="38" t="inlineStr">
         <is>
-          <t>Auto5 Count</t>
+          <t>Alarm Code</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="38" t="n">
-        <v>66027</v>
+        <v>66020</v>
       </c>
       <c r="B73" s="38" t="inlineStr">
         <is>
-          <t>Auto6 Count</t>
+          <t>Total IC</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="52" t="n">
-        <v>66030</v>
-      </c>
-      <c r="B74" s="55" t="inlineStr">
-        <is>
-          <t>Active Lot Count</t>
+      <c r="A74" s="38" t="n">
+        <v>66021</v>
+      </c>
+      <c r="B74" s="38" t="inlineStr">
+        <is>
+          <t>Total Sorted</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="52" t="n">
-        <v>66031</v>
+        <v>66030</v>
       </c>
       <c r="B75" s="55" t="inlineStr">
         <is>
-          <t>Current Lot ID</t>
+          <t>Active Lot Count</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="52" t="n">
+        <v>66031</v>
+      </c>
+      <c r="B76" s="55" t="inlineStr">
+        <is>
+          <t>Current Lot ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="52" t="n">
         <v>66032</v>
       </c>
-      <c r="B76" s="55" t="inlineStr">
+      <c r="B77" s="55" t="inlineStr">
         <is>
           <t>Sort Mode</t>
         </is>
@@ -3932,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E276"/>
+  <dimension ref="A1:E293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="7" customWidth="1" style="8" min="1" max="1"/>
@@ -9893,7 +10167,7 @@
       </c>
       <c r="E273" s="18" t="inlineStr">
         <is>
-          <t>AMR 要料</t>
+          <t>AMR 要料。〔20260803 名稱更正:S1F24 回的 CENAME 原為本機自用字串，已改為與貴端機台一致，號碼與行為不變〕</t>
         </is>
       </c>
     </row>
@@ -9918,7 +10192,7 @@
       </c>
       <c r="E274" s="18" t="inlineStr">
         <is>
-          <t>AMR 交握中(Ready)</t>
+          <t>AMR 交握中(Ready)。〔20260803 名稱更正:S1F24 回的 CENAME 原為本機自用字串，已改為與貴端機台一致，號碼與行為不變〕</t>
         </is>
       </c>
     </row>
@@ -9943,7 +10217,7 @@
       </c>
       <c r="E275" s="18" t="inlineStr">
         <is>
-          <t>AMR 上/下料完成</t>
+          <t>AMR 上/下料完成。〔20260803 名稱更正:S1F24 回的 CENAME 原為本機自用字串，已改為與貴端機台一致，號碼與行為不變〕</t>
         </is>
       </c>
     </row>
@@ -9968,7 +10242,364 @@
       </c>
       <c r="E276" s="18" t="inlineStr">
         <is>
-          <t>Color CCD 讀到身分盤 2D 後立即上傳</t>
+          <t>Color CCD 讀到身分盤 2D 後立即上傳。〔20260803 名稱更正:S1F24 回的 CENAME 原為本機自用字串，已改為與貴端機台一致，號碼與行為不變〕</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="19" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="20" t="inlineStr">
+        <is>
+          <t>Loader_Buffer_NoTray</t>
+        </is>
+      </c>
+      <c r="C277" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D277" s="20" t="n"/>
+      <c r="E277" s="20" t="inlineStr">
+        <is>
+          <t>Loader 緩衝區無盤。本機有此感測，尚未接發射點</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="19" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="20" t="inlineStr">
+        <is>
+          <t>OutputPort1BinCode</t>
+        </is>
+      </c>
+      <c r="C278" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D278" s="20" t="n"/>
+      <c r="E278" s="20" t="inlineStr">
+        <is>
+          <t>Auto1 出料站 Bin code。本機機構上做得到，尚未接發射點(酬載需雙方確認)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="19" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="20" t="inlineStr">
+        <is>
+          <t>OutputPort2BinCode</t>
+        </is>
+      </c>
+      <c r="C279" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D279" s="20" t="n"/>
+      <c r="E279" s="20" t="inlineStr">
+        <is>
+          <t>Auto2 出料站 Bin code。同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="19" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="20" t="inlineStr">
+        <is>
+          <t>OutputPort3BinCode</t>
+        </is>
+      </c>
+      <c r="C280" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D280" s="20" t="n"/>
+      <c r="E280" s="20" t="inlineStr">
+        <is>
+          <t>Auto3 出料站 Bin code。同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="19" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="20" t="inlineStr">
+        <is>
+          <t>OutputPort4BinCode</t>
+        </is>
+      </c>
+      <c r="C281" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D281" s="20" t="n"/>
+      <c r="E281" s="20" t="inlineStr">
+        <is>
+          <t>Auto4 出料站 Bin code。同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="19" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="20" t="inlineStr">
+        <is>
+          <t>OutputPort5BinCode</t>
+        </is>
+      </c>
+      <c r="C282" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D282" s="20" t="n"/>
+      <c r="E282" s="20" t="inlineStr">
+        <is>
+          <t>Auto5 出料站 Bin code。同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="19" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="20" t="inlineStr">
+        <is>
+          <t>OutputPort6BinCode</t>
+        </is>
+      </c>
+      <c r="C283" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D283" s="20" t="n"/>
+      <c r="E283" s="20" t="inlineStr">
+        <is>
+          <t>Auto6 出料站 Bin code。同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="19" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="20" t="inlineStr">
+        <is>
+          <t>MaterialModeChange</t>
+        </is>
+      </c>
+      <c r="C284" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D284" s="20" t="n"/>
+      <c r="E284" s="20" t="inlineStr">
+        <is>
+          <t>貴端機台有、本機無對應流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="19" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="20" t="inlineStr">
+        <is>
+          <t>PortStateUpdated</t>
+        </is>
+      </c>
+      <c r="C285" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D285" s="20" t="n"/>
+      <c r="E285" s="20" t="inlineStr">
+        <is>
+          <t>貴端機台有、本機無對應流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="19" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="20" t="inlineStr">
+        <is>
+          <t>UnloaderTrayIDReadOK</t>
+        </is>
+      </c>
+      <c r="C286" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D286" s="20" t="n"/>
+      <c r="E286" s="20" t="inlineStr">
+        <is>
+          <t>出料盤 2D 讀取成功。本機有此機構，尚未接發射點</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="19" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="20" t="inlineStr">
+        <is>
+          <t>UnloaderTrayIDReadFail</t>
+        </is>
+      </c>
+      <c r="C287" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D287" s="20" t="n"/>
+      <c r="E287" s="20" t="inlineStr">
+        <is>
+          <t>出料盤 2D 讀取失敗。同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="19" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="20" t="inlineStr">
+        <is>
+          <t>LoaderTrayIDReadFail</t>
+        </is>
+      </c>
+      <c r="C288" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D288" s="20" t="n"/>
+      <c r="E288" s="20" t="inlineStr">
+        <is>
+          <t>Loader 側身分盤 2D 讀取失敗。同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="19" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="20" t="inlineStr">
+        <is>
+          <t>MaximumOutputPortReport</t>
+        </is>
+      </c>
+      <c r="C289" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D289" s="20" t="n"/>
+      <c r="E289" s="20" t="inlineStr">
+        <is>
+          <t>貴端機台有、本機無對應流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="19" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="20" t="inlineStr">
+        <is>
+          <t>RunCheckRequest</t>
+        </is>
+      </c>
+      <c r="C290" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D290" s="20" t="n"/>
+      <c r="E290" s="20" t="inlineStr">
+        <is>
+          <t>測前查檢請求。本機無「測前」概念(見功能表 Remote Control #13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="19" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="20" t="inlineStr">
+        <is>
+          <t>AGVLDUnLDFinish</t>
+        </is>
+      </c>
+      <c r="C291" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D291" s="20" t="n"/>
+      <c r="E291" s="20" t="inlineStr">
+        <is>
+          <t>⚠ 與 CEID 274 在貴端機台上同名。本機的 AMR 交握走 272-275，本號不發射</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="19" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="20" t="inlineStr">
+        <is>
+          <t>AGVLdID</t>
+        </is>
+      </c>
+      <c r="C292" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D292" s="20" t="n"/>
+      <c r="E292" s="20" t="inlineStr">
+        <is>
+          <t>⚠ 與 CEID 275 同名。同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="19" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="20" t="inlineStr">
+        <is>
+          <t>DoSecsGemIndexFail</t>
+        </is>
+      </c>
+      <c r="C293" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D293" s="20" t="n"/>
+      <c r="E293" s="20" t="inlineStr">
+        <is>
+          <t>⚠ 與 CEID 251 同概念(SECS/GEM 連續失敗)。本機不發射</t>
         </is>
       </c>
     </row>
